--- a/src/订单/单子-姚足球-V2/result/lstm.xlsx
+++ b/src/订单/单子-姚足球-V2/result/lstm.xlsx
@@ -1,57 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Test Score: %.2f RMSE</t>
-  </si>
-  <si>
-    <t>Test Score: %.2f MAE</t>
-  </si>
-  <si>
-    <t>Train Score: %.2f R2</t>
-  </si>
-  <si>
-    <t>Train Score: %.2f MAPE</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -66,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -382,39 +420,83 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Score: %.2f RMSE</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Test Score: %.2f MAE</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Score: %.2f R2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Test Score: %.2f MAPE</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Train Score: %.2f RMSE</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Train Score: %.2f MAE</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Train Score: %.2f R2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Train Score: %.2f MAPE</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>67.76492055901615</v>
-      </c>
-      <c r="B2">
-        <v>53.80237479967951</v>
-      </c>
-      <c r="C2">
-        <v>0.9114144498505259</v>
-      </c>
-      <c r="D2">
-        <v>0.01528751237840555</v>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>98.58054317571235</v>
+      </c>
+      <c r="B2" t="n">
+        <v>80.04045692328833</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.8113982101571984</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.02314804607511011</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.20594738160641</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.62442231255866</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9929972920632191</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.007414026327895445</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
--- a/src/订单/单子-姚足球-V2/result/lstm.xlsx
+++ b/src/订单/单子-姚足球-V2/result/lstm.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -472,31 +472,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98.58054317571235</v>
+        <v>87.82881039489037</v>
       </c>
       <c r="B2" t="n">
-        <v>80.04045692328833</v>
+        <v>72.92410318192528</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8113982101571984</v>
+        <v>0.8502946236939309</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02314804607511011</v>
+        <v>0.02100287816975264</v>
       </c>
       <c r="E2" t="n">
-        <v>43.20594738160641</v>
+        <v>41.34499557686933</v>
       </c>
       <c r="F2" t="n">
-        <v>32.62442231255866</v>
+        <v>29.90547480004301</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9929972920632191</v>
+        <v>0.9935875373529596</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007414026327895445</v>
+        <v>0.006823573667666104</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/src/订单/单子-姚足球-V2/result/lstm.xlsx
+++ b/src/订单/单子-姚足球-V2/result/lstm.xlsx
@@ -472,28 +472,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87.82881039489037</v>
+        <v>70.93650651210555</v>
       </c>
       <c r="B2" t="n">
-        <v>72.92410318192528</v>
+        <v>56.70400930433419</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8502946236939309</v>
+        <v>0.9023430875624162</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02100287816975264</v>
+        <v>0.01635874358343404</v>
       </c>
       <c r="E2" t="n">
-        <v>41.34499557686933</v>
+        <v>42.04745690987114</v>
       </c>
       <c r="F2" t="n">
-        <v>29.90547480004301</v>
+        <v>30.27883591061091</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9935875373529596</v>
+        <v>0.9933677877402209</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006823573667666104</v>
+        <v>0.006856000013034482</v>
       </c>
     </row>
   </sheetData>
